--- a/laptop_phongvu_all.xlsx
+++ b/laptop_phongvu_all.xlsx
@@ -789,11 +789,7 @@
           <t>96.990.000 ₫</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
@@ -1172,11 +1168,7 @@
           <t>27.990.000 ₫</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
@@ -1687,11 +1679,7 @@
           <t>21.990.000 ₫</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
@@ -2076,11 +2064,7 @@
           <t>52.990.000 ₫</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
@@ -2138,11 +2122,7 @@
           <t>82.990.000 ₫</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
@@ -2330,11 +2310,7 @@
           <t>34.990.000 ₫</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
@@ -2838,11 +2814,7 @@
           <t>33.990.000 ₫</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
@@ -3286,11 +3258,7 @@
           <t>23.990.000 ₫</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
@@ -3463,11 +3431,7 @@
           <t>32.990.000 ₫</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
@@ -4231,11 +4195,7 @@
           <t>139.990.000 ₫</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
@@ -5181,11 +5141,7 @@
           <t>26.490.000 ₫</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
@@ -5435,11 +5391,7 @@
           <t>41.990.000 ₫</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
@@ -5614,11 +5566,7 @@
           <t>22.990.000 ₫</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
@@ -5675,11 +5623,7 @@
           <t>38.990.000 ₫</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
@@ -5800,11 +5744,7 @@
           <t>31.490.000 ₫</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
@@ -6428,11 +6368,7 @@
           <t>29.990.000 ₫</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
@@ -6487,11 +6423,7 @@
           <t>40.990.000 ₫</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
@@ -6675,11 +6607,7 @@
           <t>26.890.000 ₫</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
